--- a/data/tecnologia_medica/asistencia/asistencia_tecnología_médica.xlsx
+++ b/data/tecnologia_medica/asistencia/asistencia_tecnología_médica.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GM_Sección 1_Seminario" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MB_Sección 1_Seminario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TY_Sección 1_Seminario" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="XX_Sección 1_Seminario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="GF_Sección 1_Seminario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GM_Sección 1_Seminario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MB_Sección 1_Seminario" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TY_Sección 1_Seminario" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'GM_Sección 1_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'MB_Sección 1_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'TY_Sección 1_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'XX_Sección 1_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'GF_Sección 1_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'GM_Sección 1_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'MB_Sección 1_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'TY_Sección 1_Seminario'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: GM</t>
+          <t>Profesor: GF</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -748,7 +748,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: MB</t>
+          <t>Profesor: GM</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1000,7 +1000,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: TY</t>
+          <t>Profesor: MB</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: XX</t>
+          <t>Profesor: TY</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
